--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.64003333978198</v>
+        <v>3.191505417714571</v>
       </c>
       <c r="D2" t="n">
-        <v>20.32747010592103</v>
+        <v>3.303213892212168</v>
       </c>
       <c r="E2" t="n">
-        <v>8.38796952687893</v>
+        <v>1.363045048117826</v>
       </c>
       <c r="F2" t="n">
-        <v>8.552633442404941</v>
+        <v>1.389802934390803</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.864094286024115</v>
+        <v>0.4654153214789187</v>
       </c>
       <c r="D3" t="n">
-        <v>3.22220322111115</v>
+        <v>0.5236080234305619</v>
       </c>
       <c r="E3" t="n">
-        <v>8.38796952687893</v>
+        <v>1.363045048117826</v>
       </c>
       <c r="F3" t="n">
-        <v>8.552633442404941</v>
+        <v>1.389802934390803</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
